--- a/docs/hstt/hstt-template.xlsx
+++ b/docs/hstt/hstt-template.xlsx
@@ -1572,7 +1572,7 @@
     <col width="11.42578125" customWidth="1" min="1" max="1"/>
     <col width="43" customWidth="1" min="2" max="2"/>
     <col width="12.140625" customWidth="1" min="3" max="3"/>
-    <col width="16.28515625" customWidth="1" min="4" max="4"/>
+    <col width="16.28515625" customWidth="1" min="4" max="5"/>
     <col width="12.5703125" customWidth="1" min="6" max="6"/>
     <col width="16.85546875" customWidth="1" min="7" max="7"/>
     <col width="10.5703125" customWidth="1" min="8" max="8"/>

--- a/docs/hstt/hstt-template.xlsx
+++ b/docs/hstt/hstt-template.xlsx
@@ -886,7 +886,13 @@
     <col hidden="1" width="13" customWidth="1" min="26" max="26"/>
   </cols>
   <sheetData>
-    <row r="1"/>
+    <row r="1">
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>sheet:dntt</t>
+        </is>
+      </c>
+    </row>
     <row r="2"/>
     <row r="3" ht="16.5" customHeight="1">
       <c r="A3" s="1" t="inlineStr">
@@ -1138,7 +1144,13 @@
     <col hidden="1" width="13" customWidth="1" min="26" max="26"/>
   </cols>
   <sheetData>
-    <row r="1"/>
+    <row r="1">
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>sheet:dccn</t>
+        </is>
+      </c>
+    </row>
     <row r="2">
       <c r="A2" s="19" t="inlineStr">
         <is>
@@ -1594,6 +1606,11 @@
           <t>CỘNG HÒA XÃ HỘI CHỦ NGHĨA VIỆT NAM</t>
         </is>
       </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>sheet:gia-tri</t>
+        </is>
+      </c>
     </row>
     <row r="2" ht="15.75" customHeight="1">
       <c r="A2" s="19" t="inlineStr">
@@ -2370,7 +2387,13 @@
     <col hidden="1" width="13" customWidth="1" min="26" max="26"/>
   </cols>
   <sheetData>
-    <row r="1"/>
+    <row r="1">
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>sheet:khoi-luong</t>
+        </is>
+      </c>
+    </row>
     <row r="2"/>
     <row r="3" ht="15.75" customHeight="1">
       <c r="A3" s="19" t="inlineStr">
